--- a/ExportExcel/Update Majors Test.xlsx
+++ b/ExportExcel/Update Majors Test.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>STT</t>
   </si>
@@ -41,7 +41,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>7667 ms</t>
+    <t>5399 ms</t>
   </si>
   <si>
     <t/>
@@ -53,7 +53,7 @@
     <t>TC_UM_02</t>
   </si>
   <si>
-    <t>5561 ms</t>
+    <t>4386 ms</t>
   </si>
   <si>
     <t>UpdateMajorWithEmptyMajorAbbreviation</t>
@@ -62,52 +62,43 @@
     <t>TC_UM_03</t>
   </si>
   <si>
-    <t>6727 ms</t>
-  </si>
-  <si>
-    <t>UpdateMajorWithNoSelectTrainingProgram</t>
+    <t>4294 ms</t>
+  </si>
+  <si>
+    <t>UpdateMajorWithAllEmptyAndNoSelectTrainingProgram</t>
   </si>
   <si>
     <t>TC_UM_04</t>
   </si>
   <si>
-    <t>9108 ms</t>
-  </si>
-  <si>
-    <t>UpdateMajorWithAllEmptyAndNoSelectTrainingProgram</t>
+    <t>5174 ms</t>
+  </si>
+  <si>
+    <t>UpdateMajorWithMajorAbbreviationMore50</t>
   </si>
   <si>
     <t>TC_UM_05</t>
   </si>
   <si>
-    <t>6003 ms</t>
-  </si>
-  <si>
-    <t>UpdateMajorWithMajorAbbreviationMore50</t>
+    <t>6082 ms</t>
+  </si>
+  <si>
+    <t>UpdateMajorWithMajorNameMore255</t>
   </si>
   <si>
     <t>TC_UM_06</t>
   </si>
   <si>
-    <t>7754 ms</t>
-  </si>
-  <si>
-    <t>UpdateMajorWithMajorNameMore255</t>
+    <t>6099 ms</t>
+  </si>
+  <si>
+    <t>UpdateMajorWithMajorNameAndAbbreviationMore</t>
   </si>
   <si>
     <t>TC_UM_07</t>
   </si>
   <si>
-    <t>7132 ms</t>
-  </si>
-  <si>
-    <t>UpdateMajorWithMajorNameAndAbbreviationMore</t>
-  </si>
-  <si>
-    <t>TC_UM_08</t>
-  </si>
-  <si>
-    <t>6596 ms</t>
+    <t>5924 ms</t>
   </si>
 </sst>
 </file>
@@ -174,7 +165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
@@ -345,26 +336,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s" s="1">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
